--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -68,6 +68,81 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657225" y="323850"/>
+          <a:ext cx="9858375" cy="1028700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>                                                                    This is new sheet book</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -111,7 +186,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -146,7 +221,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -323,7 +398,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -335,5 +410,6 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>